--- a/1.0.0-ballot/CodeSystem-episodenart.xlsx
+++ b/1.0.0-ballot/CodeSystem-episodenart.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T05:55:59+00:00</t>
+    <t>2026-10-01T06:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/CodeSystem-episodenart.xlsx
+++ b/1.0.0-ballot/CodeSystem-episodenart.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T06:38:06+00:00</t>
+    <t>2026-10-01T08:23:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/CodeSystem-episodenart.xlsx
+++ b/1.0.0-ballot/CodeSystem-episodenart.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:23:16+00:00</t>
+    <t>2026-10-01T11:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/CodeSystem-episodenart.xlsx
+++ b/1.0.0-ballot/CodeSystem-episodenart.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:19:09+00:00</t>
+    <t>2026-10-01T11:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
